--- a/data/argentina/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/argentina/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>noM4eJv9</t>
+          <t>fotMKZ7K</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>02.08.2024 20:00</t>
+          <t>09.08.2024 15:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Espinoza F.
+          <t>Mastrangelo H.
  (Arg)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Estadio Marcelo Bielsa
- (Rosario)</t>
+          <t>Estadio Guillermo Laza
+ (Buenos Aires)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42 000</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6gMiRHVj</t>
+          <t>2iZ4q0z6</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Newells Old Boys</t>
+          <t>Dep. Riestra</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>p2SkCHXs</t>
+          <t>Y9yh1J7G</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Estudiantes L.P.</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nkx6zI2q</t>
+          <t>YHCv8dOE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>03.08.2024 15:00</t>
+          <t>09.08.2024 16:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gariano A.
+          <t>Trucco S.
  (Arg)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Estadio Malvinas Argentinas
- (Mendoza)</t>
+          <t>Claudio Fabian Tapia
+ (Barracas)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>42 000</t>
+          <t>4 400</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>tUAxIm6l</t>
+          <t>hW08cP6J</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>QuxS0ahA</t>
+          <t>bkDdeAvA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Argentinos Jrs</t>
+          <t>Talleres Cordoba</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,50 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pdWqnF1e</t>
+          <t>llkWcC07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>03.08.2024 15:00</t>
+          <t>09.08.2024 19:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lamolina N.
+          <t>Herrera D.
  (Arg)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Estadio José Amalfitani
- (Buenos Aires)</t>
+          <t>Estadio Julio Cesar Villagra
+ (Cordoba)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>49 540</t>
+          <t>34 830</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UsCR8gFd</t>
+          <t>Amzaty2s</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Gdfv0Zsh</t>
+          <t>lr2YMkTK</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Union de Santa Fe</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,50 +730,50 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vq1qlyXr</t>
+          <t>hMeNaYVf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>03.08.2024 17:15</t>
+          <t>09.08.2024 21:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Herrera D.
+          <t>Arasa N.
  (Arg)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Estadio Mario Alberto Kempes
- (Cordoba)</t>
+          <t>Estadio Juan Domingo Perón
+ (Avellaneda)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57 000</t>
+          <t>61 000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>bkDdeAvA</t>
+          <t>OhapHPm9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Talleres Cordoba</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8G45bXRA</t>
+          <t>jiDN9Zaj</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Gimnasia L.P.</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -804,50 +804,50 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>U9B9fwfF</t>
+          <t>trGn6zgR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>03.08.2024 19:15</t>
+          <t>10.08.2024 14:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mastrangelo H.
+          <t>Rey Hilfer L.
  (Arg)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Estadio Libertadores de América
- (Avellaneda)</t>
+          <t>Estadio Pedro Bidegain
+ (Buenos Aires)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>48 069</t>
+          <t>47 964</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UVatI5Y2</t>
+          <t>ju1xJoJd</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Independiente</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ju1xJoJd</t>
+          <t>KpqpxWko</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Atl. Tucuman</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -878,50 +878,50 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KvUIXFn2</t>
+          <t>badJ0EGl</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>03.08.2024 20:30</t>
+          <t>10.08.2024 16:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tello F.
+          <t>Ramirez N.
  (Arg)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Estadio Tomás Adolfo Duco
- (Buenos Aires)</t>
+          <t>Estadio Gigante de Arroyito
+ (Rosario)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>48 314</t>
+          <t>46 955</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>xd3lGq3F</t>
+          <t>4QmJ2LNc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Huracan</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>OhapHPm9</t>
+          <t>6gMiRHVj</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Newells Old Boys</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -952,50 +952,50 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bPuAZyIk</t>
+          <t>2iHr7GwL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>04.08.2024 15:00</t>
+          <t>10.08.2024 18:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ramirez N.
+          <t>Tello F.
  (Arg)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Estadio Eva Peron
- (Junin)</t>
+          <t>Estadio Juan Bautista Gargantini
+ (Mendoza)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22 000</t>
+          <t>24 000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>KQ6kGfyc</t>
+          <t>Eg51aDC4</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sarmiento Junin</t>
+          <t>Ind. Rivadavia</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Amzaty2s</t>
+          <t>hMrWAFH0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1026,50 +1026,50 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>tlVEYeXe</t>
+          <t>WCfRbho1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>04.08.2024 15:00</t>
+          <t>10.08.2024 20:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Echavarria P.
+          <t>Echenique F.
  (Arg)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Estadio 15 de Abril
- (Santa Fe)</t>
+          <t>Estadio Monumental
+ (Buenos Aires)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>27 358</t>
+          <t>84 567</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lr2YMkTK</t>
+          <t>EVqSBe2f</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Union de Santa Fe</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EVqSBe2f</t>
+          <t>xd3lGq3F</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Huracan</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1100,50 +1100,50 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>xzFHhHOR</t>
+          <t>vJVmoZG1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>04.08.2024 17:30</t>
+          <t>11.08.2024 15:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Echenique F.
+          <t>Espinoza F.
  (Arg)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Estadio Alberto J. Armando
- (Buenos Aires)</t>
+          <t>Estadio Unico Madre de Ciudades
+ (Santiago del Estero)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>57 200</t>
+          <t>42 000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>hMrWAFH0</t>
+          <t>0dHZReql</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Central Cordoba</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>hW08cP6J</t>
+          <t>Gdfv0Zsh</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1174,50 +1174,50 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rDFDgc9L</t>
+          <t>fRDz9x98</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>04.08.2024 20:00</t>
+          <t>11.08.2024 15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Arasa N.
+          <t>Balino J.
  (Arg)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Estadio Monumental Jose Fierro
- (Tucuman)</t>
+          <t>Estadio Presidente Peron
+ (Cordoba)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35 200</t>
+          <t>26 000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>KpqpxWko</t>
+          <t>8G45bXRA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Atl. Tucuman</t>
+          <t>Instituto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Eg51aDC4</t>
+          <t>80MMdBdN</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Ind. Rivadavia</t>
+          <t>Platense</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1248,12 +1248,12 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>U9kvubfS</t>
+          <t>hMZipgW7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>04.08.2024 20:00</t>
+          <t>11.08.2024 17:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1264,34 +1264,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Estadio Ciudad de Lanús – Néstor Díaz Pérez
- (Lanús)</t>
+          <t>Estadio Florencio Sola
+ (Buenos Aires)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>47 090</t>
+          <t>34 902</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Y9yh1J7G</t>
+          <t>GIb40wNM</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>nkwO1uw4</t>
+          <t>UsCR8gFd</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1322,50 +1322,50 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>jJjztvuM</t>
+          <t>nPhF1f1r</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>05.08.2024 14:30</t>
+          <t>11.08.2024 20:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rey Hilfer L.
+          <t>Zunino S.
  (Arg)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Estadio Guillermo Laza
- (Buenos Aires)</t>
+          <t>Estadio Jorge Luis Hirschi
+ (La Plata)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3 000</t>
+          <t>32 530</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2iZ4q0z6</t>
+          <t>p2SkCHXs</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Dep. Riestra</t>
+          <t>Estudiantes L.P.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0dHZReql</t>
+          <t>UVatI5Y2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Central Cordoba</t>
+          <t>Independiente</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1396,50 +1396,45 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8fN0daP2</t>
+          <t>trxILFhE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>05.08.2024 17:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Zunino S.
- (Arg)</t>
-        </is>
-      </c>
+          <t>12.08.2024 19:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Estadio Juan Carmelo Zerillo
- (La Plata)</t>
+          <t>Estadio José Dellagiovanna
+ (Buenos Aires)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21 500</t>
+          <t>26 282</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jiDN9Zaj</t>
+          <t>nkwO1uw4</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Gimnasia L.P.</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4QmJ2LNc</t>
+          <t>tUAxIm6l</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1470,60 +1465,55 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>65Xumenk</t>
+          <t>Y9EiyTMr</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>05.08.2024 20:00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Penel A.
- (Arg)</t>
-        </is>
-      </c>
+          <t>14.08.2024 19:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Estadio Ciudad de Vicente López
- (Buenos Aires)</t>
+          <t>Estadio Libertadores de América
+ (Avellaneda)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>28 530</t>
+          <t>48 069</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>80MMdBdN</t>
+          <t>QuxS0ahA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Platense</t>
+          <t>Argentinos Jrs</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>GIb40wNM</t>
+          <t>xd3lGq3F</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Huracan</t>
         </is>
       </c>
       <c r="K15" t="n">
         <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1537,62 +1527,62 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Liga Profesional</t>
+          <t>Copa Argentina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SvlzcWFD</t>
+          <t>fgvPVMI8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>08.08.2024 15:00</t>
+          <t>15.08.2024 17:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Estadio Diego Armando Maradona
- (Buenos Aires)</t>
+          <t>Estadio Centenario Ciudad de Quilmes
+ (Quilmes)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26 000</t>
+          <t>30 200</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>QuxS0ahA</t>
+          <t>ABogdBtb</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Argentinos Jrs</t>
+          <t>Talleres (R.E)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>KQ6kGfyc</t>
+          <t>GIb40wNM</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Sarmiento Junin</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="K16" t="n">
         <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1605,75 +1595,6 @@
         </is>
       </c>
       <c r="P16" t="inlineStr">
-        <is>
-          <t>Liga Profesional</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ngdGLTFj</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>06.08.2024 21:10</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Estadio Libertadores de América
- (Avellaneda)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>48 069</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ju1xJoJd</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>San Lorenzo</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>UsCR8gFd</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Velez Sarsfield</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>6</v>
-      </c>
-      <c r="L17" t="n">
-        <v>64</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>argentina</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
         <is>
           <t>Copa Argentina</t>
         </is>
